--- a/AAII_Financials/Yearly/TBVPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TBVPY_YR_FIN.xlsx
@@ -905,10 +905,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>318700</v>
+        <v>252200</v>
       </c>
       <c r="E15" s="3">
-        <v>315500</v>
+        <v>247000</v>
       </c>
       <c r="F15" s="3">
         <v>213000</v>
@@ -1050,10 +1050,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1755400</v>
+        <v>1688900</v>
       </c>
       <c r="E21" s="3">
-        <v>1905300</v>
+        <v>1836800</v>
       </c>
       <c r="F21" s="3">
         <v>1480600</v>
@@ -1593,10 +1593,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1800</v>
+        <v>13500</v>
       </c>
       <c r="E42" s="3">
-        <v>1800</v>
+        <v>48400</v>
       </c>
       <c r="F42" s="3">
         <v>31900</v>
@@ -1623,10 +1623,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>625700</v>
+        <v>549900</v>
       </c>
       <c r="E43" s="3">
-        <v>835900</v>
+        <v>568200</v>
       </c>
       <c r="F43" s="3">
         <v>542600</v>
@@ -1683,10 +1683,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>62200</v>
+        <v>90600</v>
       </c>
       <c r="E45" s="3">
-        <v>30000</v>
+        <v>108100</v>
       </c>
       <c r="F45" s="3">
         <v>28300</v>
@@ -2071,10 +2071,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>562600</v>
+        <v>523500</v>
       </c>
       <c r="E59" s="3">
-        <v>583500</v>
+        <v>547200</v>
       </c>
       <c r="F59" s="3">
         <v>534800</v>
@@ -2704,10 +2704,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>318600</v>
+        <v>295500</v>
       </c>
       <c r="E83" s="3">
-        <v>315400</v>
+        <v>289800</v>
       </c>
       <c r="F83" s="3">
         <v>251900</v>
